--- a/Relatórios/EDOC/edoc_opcao4.xlsx
+++ b/Relatórios/EDOC/edoc_opcao4.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="36">
   <si>
     <t>1</t>
   </si>
@@ -19,13 +19,13 @@
     <t/>
   </si>
   <si>
-    <t>41260429819557000130550010000257961184813727</t>
-  </si>
-  <si>
-    <t>Recebimento ignorado</t>
-  </si>
-  <si>
-    <t>Brasil cancelamento entrada</t>
+    <t>41260429107425000186550010000277941208073320</t>
+  </si>
+  <si>
+    <t>Concluído</t>
+  </si>
+  <si>
+    <t>Brasil Retorno de Armazenagem</t>
   </si>
   <si>
     <t>1001</t>
@@ -34,7 +34,49 @@
     <t>8541</t>
   </si>
   <si>
+    <t>B2B</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>41260401201578003275550320002983411963283414</t>
+  </si>
+  <si>
     <t>B2G</t>
+  </si>
+  <si>
+    <t>41260429107425000186550010000277951741438168</t>
+  </si>
+  <si>
+    <t>41260429107425000186550010000277961826424924</t>
+  </si>
+  <si>
+    <t>41260401201578003275550320002983421963283420</t>
+  </si>
+  <si>
+    <t>41260401201578003275550320002983431963283435</t>
+  </si>
+  <si>
+    <t>41260401201578003275550320002983451963283456</t>
+  </si>
+  <si>
+    <t>41260401201578003275550320002983491963283498</t>
+  </si>
+  <si>
+    <t>41260401201578003275550320002983481963283482</t>
+  </si>
+  <si>
+    <t>41260429107425000186550010000277991997830740</t>
+  </si>
+  <si>
+    <t>41260429107425000186550010000278001144920638</t>
+  </si>
+  <si>
+    <t>41260429107425000186550010000277981359978916</t>
+  </si>
+  <si>
+    <t>41260401201578003275550320002983441963283440</t>
   </si>
   <si>
     <t>Série de dados</t>
@@ -204,7 +246,595 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="Picture@5D@" descr="@5D@"/>
+        <xdr:cNvPr id="0" name="Picture@5B@" descr="@5B@"/>
+        <xdr:cNvPicPr preferRelativeResize="0">
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="5334000" y="161925"/>
+          <a:ext cx="152400" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="Picture@5B@" descr="@5B@"/>
+        <xdr:cNvPicPr preferRelativeResize="0">
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="5334000" y="161925"/>
+          <a:ext cx="152400" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture@5B@" descr="@5B@"/>
+        <xdr:cNvPicPr preferRelativeResize="0">
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="5334000" y="161925"/>
+          <a:ext cx="152400" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture@5B@" descr="@5B@"/>
+        <xdr:cNvPicPr preferRelativeResize="0">
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="5334000" y="161925"/>
+          <a:ext cx="152400" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture@5B@" descr="@5B@"/>
+        <xdr:cNvPicPr preferRelativeResize="0">
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="5334000" y="161925"/>
+          <a:ext cx="152400" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture@5B@" descr="@5B@"/>
+        <xdr:cNvPicPr preferRelativeResize="0">
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="5334000" y="161925"/>
+          <a:ext cx="152400" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture@5B@" descr="@5B@"/>
+        <xdr:cNvPicPr preferRelativeResize="0">
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="5334000" y="161925"/>
+          <a:ext cx="152400" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture@5B@" descr="@5B@"/>
+        <xdr:cNvPicPr preferRelativeResize="0">
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="5334000" y="161925"/>
+          <a:ext cx="152400" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Picture@5B@" descr="@5B@"/>
+        <xdr:cNvPicPr preferRelativeResize="0">
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="5334000" y="161925"/>
+          <a:ext cx="152400" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Picture@5B@" descr="@5B@"/>
+        <xdr:cNvPicPr preferRelativeResize="0">
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="5334000" y="161925"/>
+          <a:ext cx="152400" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Picture@5B@" descr="@5B@"/>
+        <xdr:cNvPicPr preferRelativeResize="0">
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="5334000" y="161925"/>
+          <a:ext cx="152400" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Picture@5B@" descr="@5B@"/>
+        <xdr:cNvPicPr preferRelativeResize="0">
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="5334000" y="161925"/>
+          <a:ext cx="152400" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="Picture@5B@" descr="@5B@"/>
         <xdr:cNvPicPr preferRelativeResize="0">
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
@@ -243,7 +873,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" bestFit="1" width="10" customWidth="1"/>
@@ -252,8 +882,8 @@
     <col min="4" max="4" bestFit="1" width="13" customWidth="1"/>
     <col min="5" max="5" bestFit="1" width="46" customWidth="1"/>
     <col min="6" max="6" bestFit="1" width="17" customWidth="1"/>
-    <col min="7" max="7" bestFit="1" width="22" customWidth="1"/>
-    <col min="8" max="8" bestFit="1" width="29" customWidth="1"/>
+    <col min="7" max="7" bestFit="1" width="19" customWidth="1"/>
+    <col min="8" max="8" bestFit="1" width="31" customWidth="1"/>
     <col min="9" max="9" bestFit="1" width="9" customWidth="1"/>
     <col min="10" max="10" bestFit="1" width="8" customWidth="1"/>
     <col min="11" max="11" bestFit="1" width="6" customWidth="1"/>
@@ -264,46 +894,46 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="6" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="14" customHeight="1">
@@ -317,13 +947,13 @@
         <v>1</v>
       </c>
       <c r="D2" s="3">
-        <v>46121</v>
+        <v>46123</v>
       </c>
       <c r="E2" t="s">
         <v>2</v>
       </c>
       <c r="F2" s="3">
-        <v>46121</v>
+        <v>46123</v>
       </c>
       <c r="G2" t="s">
         <v>3</v>
@@ -344,10 +974,538 @@
         <v>1</v>
       </c>
       <c r="M2" s="5">
-        <v>0.50583333333333</v>
+        <v>0 </v>
       </c>
       <c r="N2" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="14" customHeight="1">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3">
+        <v>46123</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="3">
+        <v>46123</v>
+      </c>
+      <c r="G3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K3" s="4">
+        <v>0.00</v>
+      </c>
+      <c r="L3" t="s">
+        <v>1</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0.45625000000000</v>
+      </c>
+      <c r="N3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="14" customHeight="1">
+      <c r="A4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3">
+        <v>46123</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="3">
+        <v>46123</v>
+      </c>
+      <c r="G4" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4" t="s">
+        <v>4</v>
+      </c>
+      <c r="I4" t="s">
+        <v>5</v>
+      </c>
+      <c r="J4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K4" s="4">
+        <v>0.00</v>
+      </c>
+      <c r="L4" t="s">
+        <v>1</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0 </v>
+      </c>
+      <c r="N4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="14" customHeight="1">
+      <c r="A5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3">
+        <v>46123</v>
+      </c>
+      <c r="E5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="3">
+        <v>46123</v>
+      </c>
+      <c r="G5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H5" t="s">
+        <v>4</v>
+      </c>
+      <c r="I5" t="s">
+        <v>5</v>
+      </c>
+      <c r="J5" t="s">
+        <v>6</v>
+      </c>
+      <c r="K5" s="4">
+        <v>0.00</v>
+      </c>
+      <c r="L5" t="s">
+        <v>1</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0 </v>
+      </c>
+      <c r="N5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="14" customHeight="1">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="3">
+        <v>46123</v>
+      </c>
+      <c r="E6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="3">
+        <v>46123</v>
+      </c>
+      <c r="G6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H6" t="s">
+        <v>4</v>
+      </c>
+      <c r="I6" t="s">
+        <v>5</v>
+      </c>
+      <c r="J6" t="s">
+        <v>6</v>
+      </c>
+      <c r="K6" s="4">
+        <v>0.00</v>
+      </c>
+      <c r="L6" t="s">
+        <v>1</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0.47916666666667</v>
+      </c>
+      <c r="N6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="14" customHeight="1">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="3">
+        <v>46123</v>
+      </c>
+      <c r="E7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="3">
+        <v>46123</v>
+      </c>
+      <c r="G7" t="s">
+        <v>3</v>
+      </c>
+      <c r="H7" t="s">
+        <v>4</v>
+      </c>
+      <c r="I7" t="s">
+        <v>5</v>
+      </c>
+      <c r="J7" t="s">
+        <v>6</v>
+      </c>
+      <c r="K7" s="4">
+        <v>0.00</v>
+      </c>
+      <c r="L7" t="s">
+        <v>1</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0.52152777777778</v>
+      </c>
+      <c r="N7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="14" customHeight="1">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="3">
+        <v>46123</v>
+      </c>
+      <c r="E8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="3">
+        <v>46123</v>
+      </c>
+      <c r="G8" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8" t="s">
+        <v>4</v>
+      </c>
+      <c r="I8" t="s">
+        <v>5</v>
+      </c>
+      <c r="J8" t="s">
+        <v>6</v>
+      </c>
+      <c r="K8" s="4">
+        <v>0.00</v>
+      </c>
+      <c r="L8" t="s">
+        <v>1</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0.60972222222222</v>
+      </c>
+      <c r="N8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="14" customHeight="1">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" s="3">
+        <v>46123</v>
+      </c>
+      <c r="E9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" s="3">
+        <v>46123</v>
+      </c>
+      <c r="G9" t="s">
+        <v>3</v>
+      </c>
+      <c r="H9" t="s">
+        <v>4</v>
+      </c>
+      <c r="I9" t="s">
+        <v>5</v>
+      </c>
+      <c r="J9" t="s">
+        <v>6</v>
+      </c>
+      <c r="K9" s="4">
+        <v>0.00</v>
+      </c>
+      <c r="L9" t="s">
+        <v>1</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0.73194444444444</v>
+      </c>
+      <c r="N9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="14" customHeight="1">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" t="s">
+        <v>1</v>
+      </c>
+      <c r="D10" s="3">
+        <v>46123</v>
+      </c>
+      <c r="E10" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" s="3">
+        <v>46123</v>
+      </c>
+      <c r="G10" t="s">
+        <v>3</v>
+      </c>
+      <c r="H10" t="s">
+        <v>4</v>
+      </c>
+      <c r="I10" t="s">
+        <v>5</v>
+      </c>
+      <c r="J10" t="s">
+        <v>6</v>
+      </c>
+      <c r="K10" s="4">
+        <v>0.00</v>
+      </c>
+      <c r="L10" t="s">
+        <v>1</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0.72986111111111</v>
+      </c>
+      <c r="N10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="14" customHeight="1">
+      <c r="A11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D11" s="3">
+        <v>46123</v>
+      </c>
+      <c r="E11" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11" s="3">
+        <v>46123</v>
+      </c>
+      <c r="G11" t="s">
+        <v>3</v>
+      </c>
+      <c r="H11" t="s">
+        <v>4</v>
+      </c>
+      <c r="I11" t="s">
+        <v>5</v>
+      </c>
+      <c r="J11" t="s">
+        <v>6</v>
+      </c>
+      <c r="K11" s="4">
+        <v>0.00</v>
+      </c>
+      <c r="L11" t="s">
+        <v>1</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0 </v>
+      </c>
+      <c r="N11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="14" customHeight="1">
+      <c r="A12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" t="s">
+        <v>1</v>
+      </c>
+      <c r="D12" s="3">
+        <v>46123</v>
+      </c>
+      <c r="E12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" s="3">
+        <v>46123</v>
+      </c>
+      <c r="G12" t="s">
+        <v>3</v>
+      </c>
+      <c r="H12" t="s">
+        <v>4</v>
+      </c>
+      <c r="I12" t="s">
+        <v>5</v>
+      </c>
+      <c r="J12" t="s">
+        <v>6</v>
+      </c>
+      <c r="K12" s="4">
+        <v>0.00</v>
+      </c>
+      <c r="L12" t="s">
+        <v>1</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0 </v>
+      </c>
+      <c r="N12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="14" customHeight="1">
+      <c r="A13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" t="s">
+        <v>1</v>
+      </c>
+      <c r="D13" s="3">
+        <v>46123</v>
+      </c>
+      <c r="E13" t="s">
+        <v>20</v>
+      </c>
+      <c r="F13" s="3">
+        <v>46123</v>
+      </c>
+      <c r="G13" t="s">
+        <v>3</v>
+      </c>
+      <c r="H13" t="s">
+        <v>4</v>
+      </c>
+      <c r="I13" t="s">
+        <v>5</v>
+      </c>
+      <c r="J13" t="s">
+        <v>6</v>
+      </c>
+      <c r="K13" s="4">
+        <v>0.00</v>
+      </c>
+      <c r="L13" t="s">
+        <v>1</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0 </v>
+      </c>
+      <c r="N13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="14" customHeight="1">
+      <c r="A14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" t="s">
+        <v>1</v>
+      </c>
+      <c r="D14" s="3">
+        <v>46123</v>
+      </c>
+      <c r="E14" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="3">
+        <v>46123</v>
+      </c>
+      <c r="G14" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" t="s">
+        <v>4</v>
+      </c>
+      <c r="I14" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" t="s">
+        <v>6</v>
+      </c>
+      <c r="K14" s="4">
+        <v>0.00</v>
+      </c>
+      <c r="L14" t="s">
+        <v>1</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0.59583333333333</v>
+      </c>
+      <c r="N14" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
